--- a/output/graficos_dimensiones/comunal_e_rezmat_a_2021_arica y parinacota.xlsx
+++ b/output/graficos_dimensiones/comunal_e_rezmat_a_2021_arica y parinacota.xlsx
@@ -57,7 +57,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 21:46</t>
+    <t xml:space="preserve">2026-09-10 00:56</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_rezmat_a_2021_arica y parinacota.xlsx
+++ b/output/graficos_dimensiones/comunal_e_rezmat_a_2021_arica y parinacota.xlsx
@@ -57,7 +57,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 00:56</t>
+    <t xml:space="preserve">2026-09-18 11:04</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_rezmat_a_2021_arica y parinacota.xlsx
+++ b/output/graficos_dimensiones/comunal_e_rezmat_a_2021_arica y parinacota.xlsx
@@ -57,7 +57,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 11:04</t>
+    <t xml:space="preserve">2026-09-23 14:26</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -523,7 +523,9 @@
       <c r="C4" s="2" t="n">
         <v>15201</v>
       </c>
-      <c r="D4" s="2"/>
+      <c r="D4" s="2" t="n">
+        <v>2021</v>
+      </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5">
@@ -536,7 +538,9 @@
       <c r="C5" s="2" t="n">
         <v>15202</v>
       </c>
-      <c r="D5" s="2"/>
+      <c r="D5" s="2" t="n">
+        <v>2021</v>
+      </c>
       <c r="E5" s="2"/>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_e_rezmat_a_2021_arica y parinacota.xlsx
+++ b/output/graficos_dimensiones/comunal_e_rezmat_a_2021_arica y parinacota.xlsx
@@ -57,7 +57,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 14:26</t>
+    <t xml:space="preserve">2026-10-02 16:11</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_rezmat_a_2021_arica y parinacota.xlsx
+++ b/output/graficos_dimensiones/comunal_e_rezmat_a_2021_arica y parinacota.xlsx
@@ -57,7 +57,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 16:11</t>
+    <t xml:space="preserve">2026-10-05 14:51</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
